--- a/resources/templates/standard/L1200-04.xlsx
+++ b/resources/templates/standard/L1200-04.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>지그 이력 카드</t>
   </si>
@@ -725,9 +728,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -740,29 +745,29 @@
     </row>
     <row r="3" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="5"/>
     </row>
     <row r="4" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
@@ -770,7 +775,7 @@
     </row>
     <row r="6" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="14"/>
@@ -778,7 +783,7 @@
     </row>
     <row r="7" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="14"/>
@@ -786,7 +791,7 @@
     </row>
     <row r="8" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="14"/>
@@ -794,7 +799,7 @@
     </row>
     <row r="9" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="18"/>
@@ -802,7 +807,7 @@
     </row>
     <row r="10" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="20"/>
@@ -810,27 +815,27 @@
     </row>
     <row r="11" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="22"/>
     </row>
     <row r="12" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="24"/>
     </row>
     <row r="13" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="24"/>
@@ -838,7 +843,7 @@
     </row>
     <row r="14" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="26"/>
       <c r="C14" s="24"/>
@@ -846,7 +851,7 @@
     </row>
     <row r="15" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="24"/>
@@ -854,7 +859,7 @@
     </row>
     <row r="16" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="24"/>
@@ -862,7 +867,7 @@
     </row>
     <row r="17" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="24"/>
@@ -870,7 +875,7 @@
     </row>
     <row r="18" ht="26.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="24"/>
